--- a/artfynd/A 47815-2024 artfynd.xlsx
+++ b/artfynd/A 47815-2024 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>130092302</v>
       </c>
       <c r="B4" t="n">
-        <v>96950</v>
+        <v>96952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47815-2024 artfynd.xlsx
+++ b/artfynd/A 47815-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130092306</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130092298</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>130092302</v>
       </c>
       <c r="B4" t="n">
-        <v>96952</v>
+        <v>97039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47815-2024 artfynd.xlsx
+++ b/artfynd/A 47815-2024 artfynd.xlsx
@@ -675,42 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130092306</v>
+        <v>130092302</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>97231</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490914</v>
+        <v>490984</v>
       </c>
       <c r="R2" t="n">
-        <v>6709562</v>
+        <v>6709514</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -756,17 +752,13 @@
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -788,7 +780,7 @@
         <v>130092298</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,38 +887,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130092302</v>
+        <v>130092306</v>
       </c>
       <c r="B4" t="n">
-        <v>97039</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>490984</v>
+        <v>490914</v>
       </c>
       <c r="R4" t="n">
-        <v>6709514</v>
+        <v>6709562</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,13 +968,17 @@
           <t>2025-12-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47815-2024 artfynd.xlsx
+++ b/artfynd/A 47815-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092302</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092298</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,8 +1009,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130092306</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>